--- a/WBS_ISA_Support_edit.xlsx
+++ b/WBS_ISA_Support_edit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawarit.th\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78272D28-99BE-4197-AC19-E3365CE5603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB829A64-646E-4FD0-8885-CEDDD3BF79C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{32C5D2A9-1228-445E-A0B8-CE4FBD5796AA}"/>
   </bookViews>
@@ -37,15 +37,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="95">
   <si>
     <t>ปริ้น, โอม</t>
   </si>
@@ -217,7 +214,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -238,7 +235,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -248,7 +245,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -260,7 +257,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -275,7 +272,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -285,7 +282,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -298,7 +295,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -312,7 +309,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -324,7 +321,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -341,7 +338,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -351,7 +348,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -362,7 +359,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -391,9 +388,6 @@
     <t>เขียน service ที่ต้องใช้ดึงข้อมูล, และบันทึก</t>
   </si>
   <si>
-    <t>เขียน package ที่ต้องใช้ดึงข้อมูลมาแสดง</t>
-  </si>
-  <si>
     <t>เขียน package ที่ต้องใช้บันทึกข้อมูลการแก้ไข้</t>
   </si>
   <si>
@@ -407,6 +401,123 @@
   </si>
   <si>
     <t>เนื่องจากอยู่ในการทำ module แรกเลยยังไม่ได้เริ่มทำ</t>
+  </si>
+  <si>
+    <t>ออกแบบหน้า หน้าแสดง list รายการประกัน</t>
+  </si>
+  <si>
+    <t>เพิ่ม filter, การค้นหา, form การแก้ไข้ ประกัน</t>
+  </si>
+  <si>
+    <t>นำเสนอหน้า mockup ให้กับ user, พี่เลี้ยง และ ที่ปรึกษาโปรเจค</t>
+  </si>
+  <si>
+    <t xml:space="preserve">นำเสนอหน้า mockup ให้กับ user, พี่เลี้ยง และ ที่ปรึกษาโปรเจค </t>
+  </si>
+  <si>
+    <t>เพิ่มการแสดงหน้าแสดงข้อมูลที่ขาดในส่วนของรถยนต์</t>
+  </si>
+  <si>
+    <t>เริ่มการเขียน code ฝั่งหน้าบ้าน เพิ่มหน้าหน้าแสดงรายการประกัน</t>
+  </si>
+  <si>
+    <t>เพิ่ม filter, การค้นหา</t>
+  </si>
+  <si>
+    <t>getListInsurance(
+      pRecordSet out sys_refcursor,
+      pPageNo in number default 1,           -- หน้าที่ต้องการ (เริ่มที่ 1)
+      pPageSize in number default 50,        -- จำนวนแถวต่อหน้า (50 แถว)
+      pAgrCode in varchar2 default null,     -- เลขที่สัญญา
+      pRefCode in varchar2 default null,     -- เลขที่อ้างอิง
+      pFromDate in date default null,        -- วันที่เริ่มต้น
+      pToDate in date default null,          -- วันที่สิ้นสุด
+      pComCode in varchar2 default null,     -- รหัสบริษัท
+      pKindOfIns in varchar2 default null    -- ชนิดประกัน
+    ) ;</t>
+  </si>
+  <si>
+    <t>GetListInsurance</t>
+  </si>
+  <si>
+    <t>GetListMasterGet</t>
+  </si>
+  <si>
+    <t>getInsuranceByKey(
+      pRecordSet out sys_refcursor,
+      p_tran_id           IN  varchar2 DEFAULT NULL,
+      p_a_order           IN  varchar2 DEFAULT NULL,
+      p_agr_code          IN  varchar2 DEFAULT NULL,
+      p_ref_code          IN  varchar2 DEFAULT NULL,
+      p_com_code          IN  varchar2 DEFAULT NULL,
+      p_kind_of_insurance IN  varchar2 DEFAULT NULL,
+      p_ins_date          IN  date DEFAULT NULL
+    ) ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เขียน dropdown seller code, paymenthod, kindOfIns, typeOfIns ให้สามาถใช้ service ได้ </t>
+  </si>
+  <si>
+    <t>เพิ่มหน้า form maintain data ให้สามารถแสดงข้อมูลตาม key ที่ส่งไปได้</t>
+  </si>
+  <si>
+    <t>getInsuranceCoverageByKey(
+          pRecordSet          OUT SYS_REFCURSOR,
+          p_tran_id           IN  VARCHAR2 DEFAULT NULL,
+          p_a_order           IN  VARCHAR2 DEFAULT NULL,
+          p_agr_code          IN  VARCHAR2 DEFAULT NULL,
+          p_ref_code          IN  VARCHAR2 DEFAULT NULL,
+          p_com_code          IN  VARCHAR2 DEFAULT NULL,
+          p_kind_of_insurance IN  VARCHAR2 DEFAULT NULL,
+          p_ins_date          IN  DATE DEFAULT NULL
+      ) ;</t>
+  </si>
+  <si>
+    <t>GetInsuranceCoverageByKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เพิ่มหน้า form ความคุมครอง / สถานะ </t>
+  </si>
+  <si>
+    <t>แก้ไข้หน้า form ความคุมครอง / สถานะ ให้สามารถแสดงข้อมูลตาม key ที่ส่งไปได้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เพิ่มหน้า ดูรายละเอียด dialog compulsory </t>
+  </si>
+  <si>
+    <t>getCompulsoryByKey(
+            pRecordSet     out sys_refcursor,
+            p_vu           IN  VARCHAR2 DEFAULT NULL,
+            p_qmatrix      IN  VARCHAR2 DEFAULT NULL
+      ) ;</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้าแสดง list รายการประกัน, และ filter, การค้นหา ให้มันตรงกับ service</t>
+  </si>
+  <si>
+    <t>แก้ไข List แสดงรายการ, filter ให้เป็น input ที่ให้กรอกในแต่ละ column, การค้นหา, form ให้สวยขึ้น</t>
+  </si>
+  <si>
+    <t>แก้ไข หน้าให้มีข้อมูลตรงกับในฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้า ดูรายละเอียด dialog compulsory ให้สามารถใช้ service ได้</t>
+  </si>
+  <si>
+    <t>GetCompulsoryByKey</t>
+  </si>
+  <si>
+    <t>procedure getGuarantorByKey(
+                pRecordSet     out sys_refcursor,
+                p_comcode      in varchar2 default null,
+                p_refcode      in varchar2 default null
+        ) ;</t>
+  </si>
+  <si>
+    <t>GetGuarantorByKey</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้า form maintain data ที่ dropdown ผู้ค้ำประกันให้สามารถเรียกใช้ service ได้</t>
   </si>
 </sst>
 </file>
@@ -414,14 +525,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="187" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="188" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -430,14 +541,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -475,7 +586,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -571,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -589,7 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -600,7 +711,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -664,48 +775,75 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -715,46 +853,34 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1090,7 +1216,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.69921875" style="1"/>
     <col min="2" max="2" width="27.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -1101,25 +1227,25 @@
     <col min="7" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="24" t="s">
         <v>14</v>
       </c>
@@ -1139,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="134.4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1157,7 +1283,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1175,7 +1301,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="124.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="136.80000000000001" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1193,7 +1319,7 @@
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="67.2" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -1211,7 +1337,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="67.2" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>4</v>
       </c>
@@ -1229,7 +1355,7 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1262,7 +1388,7 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:G34"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="29.69921875" customWidth="1"/>
     <col min="4" max="4" width="11.69921875" customWidth="1"/>
@@ -1271,12 +1397,12 @@
     <col min="7" max="7" width="28.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -1299,7 +1425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -1320,7 +1446,7 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -1341,7 +1467,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -1362,7 +1488,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -1384,7 +1510,7 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="B8" s="30" t="s">
         <v>18</v>
@@ -1397,7 +1523,7 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="6"/>
       <c r="B9" s="30" t="s">
         <v>30</v>
@@ -1410,7 +1536,7 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="30" t="s">
         <v>31</v>
@@ -1423,7 +1549,7 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -1444,7 +1570,7 @@
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -1465,7 +1591,7 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -1486,7 +1612,7 @@
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -1505,50 +1631,50 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="28"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="28"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="28"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="28"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="28"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="28"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="28"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="28"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="28"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="28"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="28"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" s="28"/>
     </row>
   </sheetData>
@@ -1561,7 +1687,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="7" width="8.69921875" style="10"/>
@@ -1573,15 +1699,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -1590,14 +1716,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -1606,14 +1732,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -1624,15 +1750,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="63"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="52"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -1650,274 +1776,914 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
+      <c r="A7" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40"/>
       <c r="H7" s="37">
         <v>45995</v>
       </c>
       <c r="I7" s="37">
-        <v>46011</v>
-      </c>
-      <c r="J7" s="36">
+        <v>45995</v>
+      </c>
+      <c r="J7" s="15">
+        <v>1</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="37">
+        <v>45999</v>
+      </c>
+      <c r="I8" s="37">
+        <v>46002</v>
+      </c>
+      <c r="J8" s="15">
+        <v>3</v>
+      </c>
+      <c r="K8" s="16">
+        <v>1</v>
+      </c>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="I9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="J9" s="15">
+        <v>1</v>
+      </c>
+      <c r="K9" s="16">
+        <v>1</v>
+      </c>
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="37">
+        <v>46006</v>
+      </c>
+      <c r="I10" s="37">
+        <v>46007</v>
+      </c>
+      <c r="J10" s="15">
+        <v>2</v>
+      </c>
+      <c r="K10" s="16">
+        <v>1</v>
+      </c>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="37">
+        <v>46008</v>
+      </c>
+      <c r="I11" s="37">
+        <v>46009</v>
+      </c>
+      <c r="J11" s="15">
+        <v>2</v>
+      </c>
+      <c r="K11" s="16">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="37">
         <v>46010</v>
       </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="64"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="58" t="s">
+      <c r="I12" s="37">
+        <v>46010</v>
+      </c>
+      <c r="J12" s="15">
+        <v>1</v>
+      </c>
+      <c r="K12" s="16">
+        <v>1</v>
+      </c>
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="I13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="16">
+        <v>1</v>
+      </c>
+      <c r="L13" s="17"/>
+    </row>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="37">
+        <v>46013</v>
+      </c>
+      <c r="I14" s="37">
+        <v>46013</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="K14" s="16">
+        <v>1</v>
+      </c>
+      <c r="L14" s="17"/>
+    </row>
+    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="37">
+        <v>46014</v>
+      </c>
+      <c r="I15" s="37">
+        <v>46014</v>
+      </c>
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="16">
+        <v>1</v>
+      </c>
+      <c r="L15" s="17"/>
+    </row>
+    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="37">
+        <v>46016</v>
+      </c>
+      <c r="I16" s="37">
+        <v>46016</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="16">
+        <v>1</v>
+      </c>
+      <c r="L16" s="17"/>
+    </row>
+    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37">
+        <v>46017</v>
+      </c>
+      <c r="I17" s="37">
+        <v>46017</v>
+      </c>
+      <c r="J17" s="15">
+        <v>1</v>
+      </c>
+      <c r="K17" s="16">
+        <v>1</v>
+      </c>
+      <c r="L17" s="17"/>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="37">
+        <v>46020</v>
+      </c>
+      <c r="I18" s="37">
+        <v>46020</v>
+      </c>
+      <c r="J18" s="15">
+        <v>1</v>
+      </c>
+      <c r="K18" s="16">
+        <v>1</v>
+      </c>
+      <c r="L18" s="17"/>
+    </row>
+    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="37">
+        <v>46021</v>
+      </c>
+      <c r="I19" s="37">
+        <v>46021</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="16">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="37">
+        <v>46021</v>
+      </c>
+      <c r="I20" s="37">
+        <v>46021</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K20" s="16">
+        <v>1</v>
+      </c>
+      <c r="L20" s="17"/>
+    </row>
+    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="37">
+        <v>46027</v>
+      </c>
+      <c r="I21" s="37">
+        <v>46027</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="16">
+        <v>1</v>
+      </c>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="37">
+        <v>46027</v>
+      </c>
+      <c r="I22" s="37">
+        <v>46027</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1</v>
+      </c>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="37">
+        <v>46027</v>
+      </c>
+      <c r="I23" s="37">
+        <v>46027</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K23" s="16">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A25" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="37">
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="37">
         <v>46012</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I25" s="37">
         <v>46066</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J25" s="15">
+        <v>0</v>
+      </c>
+      <c r="K25" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="L25" s="17"/>
+    </row>
+    <row r="26" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="55"/>
+    </row>
+    <row r="27" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A27" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="14">
+        <v>46015</v>
+      </c>
+      <c r="I27" s="14">
+        <v>46015</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="K27" s="16">
+        <v>1</v>
+      </c>
+      <c r="L27" s="17"/>
+    </row>
+    <row r="28" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A28" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="14">
+        <v>46015</v>
+      </c>
+      <c r="I28" s="14">
+        <v>46015</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K28" s="16">
+        <v>1</v>
+      </c>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A29" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="14">
+        <v>46021</v>
+      </c>
+      <c r="I29" s="14">
+        <v>46021</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="16">
+        <v>1</v>
+      </c>
+      <c r="L29" s="17"/>
+    </row>
+    <row r="30" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A30" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I30" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1</v>
+      </c>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A31" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I31" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="K31" s="16">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17"/>
+    </row>
+    <row r="32" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A32" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="14">
+        <v>46012</v>
+      </c>
+      <c r="I32" s="14">
         <v>46066</v>
       </c>
-      <c r="K9" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-    </row>
-    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="14">
+      <c r="J32" s="15">
+        <v>0</v>
+      </c>
+      <c r="K32" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="L32" s="17"/>
+    </row>
+    <row r="33" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="55"/>
+    </row>
+    <row r="34" spans="1:12" s="71" customFormat="1" ht="228" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="68"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="14">
+        <v>46015</v>
+      </c>
+      <c r="I34" s="14">
+        <v>46380</v>
+      </c>
+      <c r="J34" s="65">
+        <v>0.5</v>
+      </c>
+      <c r="K34" s="66">
+        <v>1</v>
+      </c>
+      <c r="L34" s="70"/>
+    </row>
+    <row r="35" spans="1:12" s="71" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="14">
+        <v>46016</v>
+      </c>
+      <c r="I35" s="14">
+        <v>46016</v>
+      </c>
+      <c r="J35" s="65">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="66">
+        <v>1</v>
+      </c>
+      <c r="L35" s="70"/>
+    </row>
+    <row r="36" spans="1:12" s="71" customFormat="1" ht="215.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="14">
+        <v>46021</v>
+      </c>
+      <c r="I36" s="14">
+        <v>46021</v>
+      </c>
+      <c r="J36" s="65">
+        <v>0.2</v>
+      </c>
+      <c r="K36" s="66">
+        <v>1</v>
+      </c>
+      <c r="L36" s="70"/>
+    </row>
+    <row r="37" spans="1:12" ht="106.2" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A37" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I37" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J37" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="K37" s="66">
+        <v>1</v>
+      </c>
+      <c r="L37" s="17"/>
+    </row>
+    <row r="38" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I38" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J38" s="65">
+        <v>0.05</v>
+      </c>
+      <c r="K38" s="66">
+        <v>1</v>
+      </c>
+      <c r="L38" s="17"/>
+    </row>
+    <row r="39" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A39" s="38"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="17"/>
+    </row>
+    <row r="40" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A40" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="14">
         <v>46012</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I40" s="14">
         <v>46066</v>
       </c>
-      <c r="J11" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K11" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
-    </row>
-    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I13" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J13" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K13" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="58" t="s">
+      <c r="J40" s="15">
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <v>0</v>
+      </c>
+      <c r="L40" s="17"/>
+    </row>
+    <row r="41" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="55"/>
+    </row>
+    <row r="42" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A42" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I14" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J14" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K14" s="16">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17"/>
-    </row>
-    <row r="15" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="51"/>
-    </row>
-    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="58" t="s">
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="17"/>
+    </row>
+    <row r="43" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A43" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="17"/>
-    </row>
-    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="55"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19">
-        <f>SUM(J7:J17)</f>
-        <v>230274</v>
-      </c>
-      <c r="K18" s="20">
-        <f>AVERAGE(K7:K17)</f>
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="L18" s="21"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="17"/>
+    </row>
+    <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A44" s="56"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="19">
+        <f>SUM(J7:J43)</f>
+        <v>18.000000000000004</v>
+      </c>
+      <c r="K44" s="20">
+        <f>AVERAGE(K7:K43)</f>
+        <v>0.94666666666666666</v>
+      </c>
+      <c r="L44" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="43">
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:L12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -1941,15 +2707,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -1958,14 +2724,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -1974,14 +2740,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -1992,15 +2758,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -2018,31 +2784,31 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="14">
         <v>45995</v>
       </c>
@@ -2058,15 +2824,15 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="14">
         <v>46012</v>
       </c>
@@ -2082,31 +2848,31 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="51"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="55"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="14">
         <v>46012</v>
       </c>
@@ -2122,31 +2888,31 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="A12" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="14">
         <v>46012</v>
       </c>
@@ -2162,15 +2928,15 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="14">
         <v>46012</v>
       </c>
@@ -2186,31 +2952,31 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="55"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="A15" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -2218,13 +2984,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -2232,13 +2998,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -2291,15 +3057,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -2308,14 +3074,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -2324,14 +3090,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -2342,15 +3108,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -2368,31 +3134,31 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="14">
         <v>45995</v>
       </c>
@@ -2408,15 +3174,15 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="14">
         <v>46012</v>
       </c>
@@ -2432,31 +3198,31 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="51"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="55"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="14">
         <v>46012</v>
       </c>
@@ -2472,31 +3238,31 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="A12" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="14">
         <v>46012</v>
       </c>
@@ -2512,15 +3278,15 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="14">
         <v>46012</v>
       </c>
@@ -2536,31 +3302,31 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="55"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="A15" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -2568,13 +3334,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -2582,13 +3348,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -2630,7 +3396,7 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.09765625" customWidth="1"/>
@@ -2638,12 +3404,12 @@
     <col min="7" max="7" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -2666,7 +3432,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -2692,7 +3458,7 @@
       <c r="K4" s="27"/>
       <c r="L4" s="27"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -2717,7 +3483,7 @@
       <c r="K5" s="27"/>
       <c r="L5" s="27"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -2742,7 +3508,7 @@
       <c r="K6" s="27"/>
       <c r="L6" s="27"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -2768,7 +3534,7 @@
       <c r="K7" s="27"/>
       <c r="L7" s="27"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="B8" s="30" t="s">
         <v>32</v>
@@ -2786,7 +3552,7 @@
       <c r="K8" s="27"/>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="6"/>
       <c r="B9" s="30" t="s">
         <v>34</v>
@@ -2804,7 +3570,7 @@
       <c r="K9" s="27"/>
       <c r="L9" s="27"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="30" t="s">
         <v>33</v>
@@ -2822,7 +3588,7 @@
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -2847,7 +3613,7 @@
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -2872,7 +3638,7 @@
       <c r="K12" s="27"/>
       <c r="L12" s="27"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -2897,7 +3663,7 @@
       <c r="K13" s="27"/>
       <c r="L13" s="27"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -2920,7 +3686,7 @@
       <c r="K14" s="27"/>
       <c r="L14" s="27"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="28"/>
       <c r="D15" s="27"/>
       <c r="E15" s="27"/>
@@ -2929,66 +3695,66 @@
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H17" s="28"/>
       <c r="J17" s="28"/>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H18" s="28"/>
       <c r="J18" s="28"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="28"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="28"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="28"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="28"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="28"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="28"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="28"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="28"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="28"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" s="28"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="28"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" s="28"/>
     </row>
   </sheetData>
@@ -3013,15 +3779,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -3030,14 +3796,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -3046,14 +3812,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -3064,15 +3830,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -3090,43 +3856,45 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
+      <c r="J7" s="15">
+        <v>1</v>
+      </c>
       <c r="K7" s="16"/>
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -3134,29 +3902,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="51"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="55"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -3164,29 +3932,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -3194,13 +3962,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -3208,29 +3976,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="55"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -3238,13 +4006,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -3252,18 +4020,18 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
         <f>SUM(J7:J16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="20" t="e">
         <f>AVERAGE(K7:K16)</f>
@@ -3311,15 +4079,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -3328,14 +4096,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -3344,14 +4112,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -3362,15 +4130,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -3388,29 +4156,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="15"/>
@@ -3418,13 +4186,13 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -3432,29 +4200,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="51"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="55"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -3462,29 +4230,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -3492,13 +4260,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -3506,29 +4274,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="55"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -3536,13 +4304,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -3550,13 +4318,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -3609,15 +4377,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -3626,14 +4394,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -3642,14 +4410,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="45">
-        <v>1</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -3660,15 +4428,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -3686,29 +4454,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="15"/>
@@ -3716,13 +4484,13 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -3730,29 +4498,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="51"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="55"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -3760,29 +4528,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -3790,13 +4558,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -3804,29 +4572,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="55"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -3834,13 +4602,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -3848,13 +4616,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">

--- a/WBS_ISA_Support_edit.xlsx
+++ b/WBS_ISA_Support_edit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawarit.th\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB829A64-646E-4FD0-8885-CEDDD3BF79C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11211321-9BC9-433D-AB74-A1E20581D5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{32C5D2A9-1228-445E-A0B8-CE4FBD5796AA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{32C5D2A9-1228-445E-A0B8-CE4FBD5796AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="121">
   <si>
     <t>ปริ้น, โอม</t>
   </si>
@@ -214,7 +217,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -235,7 +238,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -245,7 +248,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -257,7 +260,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -272,7 +275,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -282,7 +285,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -295,7 +298,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -309,7 +312,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -321,7 +324,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -338,7 +341,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -348,7 +351,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <charset val="222"/>
         <scheme val="minor"/>
@@ -359,7 +362,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -379,34 +382,16 @@
     <t>พี่ไกด์</t>
   </si>
   <si>
-    <t>ออกแบบหน้า UX/UI ของระบบและ confirm กับผู้ใช้</t>
-  </si>
-  <si>
-    <t>เริ่มเขียน code หน้าบ้านตามที่ออกแบบ</t>
-  </si>
-  <si>
-    <t>เขียน service ที่ต้องใช้ดึงข้อมูล, และบันทึก</t>
-  </si>
-  <si>
-    <t>เขียน package ที่ต้องใช้บันทึกข้อมูลการแก้ไข้</t>
-  </si>
-  <si>
     <t>มีปัญหาเกี่ยวกับการเขียน html, scss โดยไม่ตรงกับที่ออกแบบ เลยต้องแก้ไข้ให้ใกล้เคียงที่สุด</t>
   </si>
   <si>
     <t>มีปัญหาเกี่ยวกับการเขียน package, service ต้องทำความเข้าใจระบบในการ query</t>
   </si>
   <si>
-    <t>ยังไม่ได้เริ่มทำ</t>
-  </si>
-  <si>
     <t>เนื่องจากอยู่ในการทำ module แรกเลยยังไม่ได้เริ่มทำ</t>
   </si>
   <si>
     <t>ออกแบบหน้า หน้าแสดง list รายการประกัน</t>
-  </si>
-  <si>
-    <t>เพิ่ม filter, การค้นหา, form การแก้ไข้ ประกัน</t>
   </si>
   <si>
     <t>นำเสนอหน้า mockup ให้กับ user, พี่เลี้ยง และ ที่ปรึกษาโปรเจค</t>
@@ -519,20 +504,125 @@
   <si>
     <t>แก้ไขหน้า form maintain data ที่ dropdown ผู้ค้ำประกันให้สามารถเรียกใช้ service ได้</t>
   </si>
+  <si>
+    <t xml:space="preserve">ออกแบบหน้า หน้าแสดง list </t>
+  </si>
+  <si>
+    <t>แก้ไขตารางให้ถูก format ในแต่ละ column</t>
+  </si>
+  <si>
+    <t>เพิ่ม filter, การค้นหา, form การแสดงข้อมูลรายละเอียด และ ปุ่ม cancel</t>
+  </si>
+  <si>
+    <t>แก้ไข form การแสดงข้อมูลให้ถูก format ในแต่ละ input ที่แสดง</t>
+  </si>
+  <si>
+    <t>เพิ่ม filter, การค้นหา, form การแก้ไข group marketing และ ปุ่ม บันทึกการแก้ไข, เพิ่ม และ ยกเลิก</t>
+  </si>
+  <si>
+    <t>เพิ่ม filter, การค้นหา, form การแก้ไข ประกัน, ปุมยืนยันการแก้ไข และ ปุ่มยกเลิก</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6/1/2026</t>
+  </si>
+  <si>
+    <t>getRdRtTransByKey(
+        pRecordSet        OUT sys_refcursor,
+        p_n_agr_code      IN  VARCHAR2 DEFAULT NULL,
+        p_o_agr_code      IN  VARCHAR2 DEFAULT NULL,
+        p_start_rd_rt_dt  IN  DATE DEFAULT NULL
+    ) ;</t>
+  </si>
+  <si>
+    <t>GetCancelByKey</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้าแสดงรายการ โครงสร้างสัญญาใหม่ ให้สามารถเรียกใช้ service ได้</t>
+  </si>
+  <si>
+    <t>getRdRtTransDetail (
+              pRecordSet        OUT sys_refcursor,
+              p_runno           in varchar2 default null,
+              p_comcode         in varchar2 default null
+      ) ;</t>
+  </si>
+  <si>
+    <t>GetCancelDetail</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้าแสดงรายละเอียดของ โครงสร้างสัญญาใหม่ ให้สามารถเรียกใช้ service ได้</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7/1/2026</t>
+  </si>
+  <si>
+    <t>เริ่มการเขียน code ฝั่งหน้าบ้าน เพิ่ม module และ เพิ่มหน้าแสดงรายการ และปุ่มยกเลิก ของโครงสร้างสัญญาใหม่</t>
+  </si>
+  <si>
+    <t>เพิ่มหน้ารายละเอียดของรายการสัญญาที่เลือก</t>
+  </si>
+  <si>
+    <t>เพิ่ม function การ check status ปุ่มไหนที่กดได้</t>
+  </si>
+  <si>
+    <t>GetCheckReceiveForCancelRT</t>
+  </si>
+  <si>
+    <t>การเช็คปุมจะเป็นการวน loop เรียก api ในแต่ละตัว</t>
+  </si>
+  <si>
+    <t>เพิ่ม alert ยืนยันการแก้ไข</t>
+  </si>
+  <si>
+    <t>ปัญหาแสดงหน้า alert อยู่ใน component ลูก</t>
+  </si>
+  <si>
+    <t>GetMarketingList(pRecordSet out sys_refcursor, pQueryType in varchar2);</t>
+  </si>
+  <si>
+    <t>GetMarketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8/1/2026</t>
+  </si>
+  <si>
+    <t>เพิ่ม module และ เพิ่มหน้า select search, fiter ,การค้นหา</t>
+  </si>
+  <si>
+    <t>แก้ไขหน้า select search, fiter ,การค้นหา ให้สามารเรียก service ได้ และ เขียน function การค้นหา</t>
+  </si>
+  <si>
+    <t>แก้ไข้ หน้าแสดงรายการประกันตอนกด dbclick ให้ปิด component แล้วไปเรียก component ลูก</t>
+  </si>
+  <si>
+    <t>เนื่องจากปัญการแสดงของ alert ที่อยู่ใน component เดียว ทำให้เมื่อมีเกิน 1 มันจะไม่มี backdrop ปิดอีก component ที่ไม่ได้เรียกใช้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เพิ่มหน้า form credit card </t>
+  </si>
+  <si>
+    <t>getBBL( pRecordSet out sys_refcursor ) ;</t>
+  </si>
+  <si>
+    <t>GetBBL</t>
+  </si>
+  <si>
+    <t>แก้ไขในหน้า maintain data ให้มีเงื่อนไขและส่งค่าไปให้ หน้า credit card check และเรียกใช้ service</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="187" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="188" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -541,14 +631,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -586,7 +676,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -682,7 +772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -700,7 +790,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -711,7 +801,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -775,6 +865,18 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -784,6 +886,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -802,13 +934,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -820,67 +952,34 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1216,7 +1315,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.69921875" style="1"/>
     <col min="2" max="2" width="27.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -1227,25 +1326,25 @@
     <col min="7" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>14</v>
       </c>
@@ -1265,7 +1364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="134.4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1283,7 +1382,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1301,7 +1400,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="136.80000000000001" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1319,7 +1418,7 @@
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="67.2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -1337,7 +1436,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="67.2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>4</v>
       </c>
@@ -1355,7 +1454,7 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1388,7 +1487,7 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:G34"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.69921875" customWidth="1"/>
     <col min="4" max="4" width="11.69921875" customWidth="1"/>
@@ -1397,12 +1496,12 @@
     <col min="7" max="7" width="28.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -1425,7 +1524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -1446,7 +1545,7 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -1467,7 +1566,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -1488,7 +1587,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -1510,7 +1609,7 @@
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="30" t="s">
         <v>18</v>
@@ -1523,7 +1622,7 @@
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="30" t="s">
         <v>30</v>
@@ -1536,7 +1635,7 @@
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="30" t="s">
         <v>31</v>
@@ -1549,7 +1648,7 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -1570,7 +1669,7 @@
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -1591,7 +1690,7 @@
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -1612,7 +1711,7 @@
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -1631,50 +1730,50 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="28"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="28"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="28"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="28"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="28"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="28"/>
     </row>
   </sheetData>
@@ -1687,7 +1786,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="7" width="8.69921875" style="10"/>
@@ -1699,15 +1798,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -1716,14 +1815,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -1732,14 +1831,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -1750,15 +1849,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="52"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="66"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -1776,31 +1875,31 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="A7" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
       <c r="H7" s="37">
         <v>45995</v>
       </c>
@@ -1808,7 +1907,7 @@
         <v>45995</v>
       </c>
       <c r="J7" s="15">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -1816,15 +1915,15 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="A8" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
       <c r="H8" s="37">
         <v>45999</v>
       </c>
@@ -1832,7 +1931,7 @@
         <v>46002</v>
       </c>
       <c r="J8" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" s="16">
         <v>1</v>
@@ -1840,15 +1939,15 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="A9" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
       <c r="H9" s="37">
         <v>46003</v>
       </c>
@@ -1856,7 +1955,7 @@
         <v>46003</v>
       </c>
       <c r="J9" s="15">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K9" s="16">
         <v>1</v>
@@ -1864,15 +1963,15 @@
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="A10" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
       <c r="H10" s="37">
         <v>46006</v>
       </c>
@@ -1880,7 +1979,7 @@
         <v>46007</v>
       </c>
       <c r="J10" s="15">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="16">
         <v>1</v>
@@ -1888,15 +1987,15 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="A11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
       <c r="H11" s="37">
         <v>46008</v>
       </c>
@@ -1904,7 +2003,7 @@
         <v>46009</v>
       </c>
       <c r="J11" s="15">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="16">
         <v>1</v>
@@ -1912,15 +2011,15 @@
       <c r="L11" s="17"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="A12" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
       <c r="H12" s="37">
         <v>46010</v>
       </c>
@@ -1928,7 +2027,7 @@
         <v>46010</v>
       </c>
       <c r="J12" s="15">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K12" s="16">
         <v>1</v>
@@ -1936,15 +2035,15 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="A13" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
       <c r="H13" s="37">
         <v>46013</v>
       </c>
@@ -1952,7 +2051,7 @@
         <v>46013</v>
       </c>
       <c r="J13" s="15">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="16">
         <v>1</v>
@@ -1960,15 +2059,15 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
+      <c r="A14" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="37">
         <v>46013</v>
       </c>
@@ -1976,7 +2075,7 @@
         <v>46013</v>
       </c>
       <c r="J14" s="15">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K14" s="16">
         <v>1</v>
@@ -1984,15 +2083,15 @@
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="37">
         <v>46014</v>
       </c>
@@ -2008,15 +2107,15 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="A16" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="37">
         <v>46016</v>
       </c>
@@ -2032,15 +2131,15 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="A17" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="37">
         <v>46017</v>
       </c>
@@ -2056,15 +2155,15 @@
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="A18" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="44"/>
       <c r="H18" s="37">
         <v>46020</v>
       </c>
@@ -2080,15 +2179,15 @@
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="A19" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="44"/>
       <c r="H19" s="37">
         <v>46021</v>
       </c>
@@ -2104,15 +2203,15 @@
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="A20" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="44"/>
       <c r="H20" s="37">
         <v>46021</v>
       </c>
@@ -2128,15 +2227,15 @@
       <c r="L20" s="17"/>
     </row>
     <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="A21" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="44"/>
       <c r="H21" s="37">
         <v>46027</v>
       </c>
@@ -2152,15 +2251,15 @@
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
+      <c r="A22" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44"/>
       <c r="H22" s="37">
         <v>46027</v>
       </c>
@@ -2176,15 +2275,15 @@
       <c r="L22" s="17"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A23" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="A23" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="44"/>
       <c r="H23" s="37">
         <v>46027</v>
       </c>
@@ -2200,93 +2299,105 @@
       <c r="L23" s="17"/>
     </row>
     <row r="24" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="17"/>
+      <c r="A24" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K24" s="16">
+        <v>1</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="25" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A25" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="37">
-        <v>46012</v>
-      </c>
-      <c r="I25" s="37">
-        <v>46066</v>
+      <c r="A25" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>112</v>
       </c>
       <c r="J25" s="15">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K25" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L25" s="17"/>
     </row>
-    <row r="26" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="53" t="s">
+    <row r="26" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A26" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K26" s="16">
+        <v>1</v>
+      </c>
+      <c r="L26" s="17"/>
+    </row>
+    <row r="27" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="55"/>
-    </row>
-    <row r="27" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A27" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="14">
-        <v>46015</v>
-      </c>
-      <c r="I27" s="14">
-        <v>46015</v>
-      </c>
-      <c r="J27" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="17"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="54"/>
     </row>
     <row r="28" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A28" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="A28" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="44"/>
       <c r="H28" s="14">
         <v>46015</v>
       </c>
@@ -2294,52 +2405,52 @@
         <v>46015</v>
       </c>
       <c r="J28" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="K28" s="16">
+        <v>1</v>
+      </c>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A29" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="14">
+        <v>46015</v>
+      </c>
+      <c r="I29" s="14">
+        <v>46015</v>
+      </c>
+      <c r="J29" s="15">
         <v>0.2</v>
       </c>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="17"/>
-    </row>
-    <row r="29" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A29" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="14">
+      <c r="K29" s="16">
+        <v>1</v>
+      </c>
+      <c r="L29" s="17"/>
+    </row>
+    <row r="30" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A30" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="14">
         <v>46021</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I30" s="14">
         <v>46021</v>
-      </c>
-      <c r="J29" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="K29" s="16">
-        <v>1</v>
-      </c>
-      <c r="L29" s="17"/>
-    </row>
-    <row r="30" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A30" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="14">
-        <v>46027</v>
-      </c>
-      <c r="I30" s="14">
-        <v>46027</v>
       </c>
       <c r="J30" s="15">
         <v>0.1</v>
@@ -2350,15 +2461,15 @@
       <c r="L30" s="17"/>
     </row>
     <row r="31" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A31" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="A31" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="14">
         <v>46027</v>
       </c>
@@ -2366,253 +2477,261 @@
         <v>46027</v>
       </c>
       <c r="J31" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K31" s="16">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17"/>
+    </row>
+    <row r="32" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A32" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I32" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J32" s="15">
         <v>0.05</v>
       </c>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="17"/>
-    </row>
-    <row r="32" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A32" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I32" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J32" s="15">
-        <v>0</v>
-      </c>
       <c r="K32" s="16">
+        <v>1</v>
+      </c>
+      <c r="L32" s="17"/>
+    </row>
+    <row r="33" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A33" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="K33" s="16">
+        <v>1</v>
+      </c>
+      <c r="L33" s="17"/>
+    </row>
+    <row r="34" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="54"/>
+    </row>
+    <row r="35" spans="1:12" s="41" customFormat="1" ht="228" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="14">
+        <v>46015</v>
+      </c>
+      <c r="I35" s="14">
+        <v>46380</v>
+      </c>
+      <c r="J35" s="38">
         <v>0.5</v>
       </c>
-      <c r="L32" s="17"/>
-    </row>
-    <row r="33" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="55"/>
-    </row>
-    <row r="34" spans="1:12" s="71" customFormat="1" ht="228" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="67" t="s">
+      <c r="K35" s="39">
+        <v>1</v>
+      </c>
+      <c r="L35" s="40"/>
+    </row>
+    <row r="36" spans="1:12" s="41" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="14">
+        <v>46016</v>
+      </c>
+      <c r="I36" s="14">
+        <v>46016</v>
+      </c>
+      <c r="J36" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="39">
+        <v>1</v>
+      </c>
+      <c r="L36" s="40"/>
+    </row>
+    <row r="37" spans="1:12" s="41" customFormat="1" ht="215.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="14">
-        <v>46015</v>
-      </c>
-      <c r="I34" s="14">
-        <v>46380</v>
-      </c>
-      <c r="J34" s="65">
-        <v>0.5</v>
-      </c>
-      <c r="K34" s="66">
-        <v>1</v>
-      </c>
-      <c r="L34" s="70"/>
-    </row>
-    <row r="35" spans="1:12" s="71" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="14">
-        <v>46016</v>
-      </c>
-      <c r="I35" s="14">
-        <v>46016</v>
-      </c>
-      <c r="J35" s="65">
-        <v>0.5</v>
-      </c>
-      <c r="K35" s="66">
-        <v>1</v>
-      </c>
-      <c r="L35" s="70"/>
-    </row>
-    <row r="36" spans="1:12" s="71" customFormat="1" ht="215.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="14">
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="14">
         <v>46021</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I37" s="14">
         <v>46021</v>
       </c>
-      <c r="J36" s="65">
+      <c r="J37" s="38">
         <v>0.2</v>
       </c>
-      <c r="K36" s="66">
-        <v>1</v>
-      </c>
-      <c r="L36" s="70"/>
-    </row>
-    <row r="37" spans="1:12" ht="106.2" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="14">
-        <v>46027</v>
-      </c>
-      <c r="I37" s="14">
-        <v>46027</v>
-      </c>
-      <c r="J37" s="65">
-        <v>0.1</v>
-      </c>
-      <c r="K37" s="66">
-        <v>1</v>
-      </c>
-      <c r="L37" s="17"/>
-    </row>
-    <row r="38" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="69"/>
+      <c r="K37" s="39">
+        <v>1</v>
+      </c>
+      <c r="L37" s="40"/>
+    </row>
+    <row r="38" spans="1:12" ht="106.2" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="14">
         <v>46027</v>
       </c>
       <c r="I38" s="14">
         <v>46027</v>
       </c>
-      <c r="J38" s="65">
+      <c r="J38" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="K38" s="39">
+        <v>1</v>
+      </c>
+      <c r="L38" s="17"/>
+    </row>
+    <row r="39" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="14">
+        <v>46027</v>
+      </c>
+      <c r="I39" s="14">
+        <v>46027</v>
+      </c>
+      <c r="J39" s="38">
         <v>0.05</v>
       </c>
-      <c r="K38" s="66">
-        <v>1</v>
-      </c>
-      <c r="L38" s="17"/>
-    </row>
-    <row r="39" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A39" s="38"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="16"/>
+      <c r="K39" s="39">
+        <v>1</v>
+      </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A40" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I40" s="14">
-        <v>46066</v>
+      <c r="A40" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="J40" s="15">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K40" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="17"/>
     </row>
-    <row r="41" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="53" t="s">
+    <row r="41" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A41" s="42"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="17"/>
+    </row>
+    <row r="42" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="55"/>
-    </row>
-    <row r="42" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A42" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="17"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A43" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="40"/>
+      <c r="A43" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="44"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="15"/>
@@ -2620,70 +2739,87 @@
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A44" s="56"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="19">
-        <f>SUM(J7:J43)</f>
-        <v>18.000000000000004</v>
-      </c>
-      <c r="K44" s="20">
-        <f>AVERAGE(K7:K43)</f>
-        <v>0.94666666666666666</v>
-      </c>
-      <c r="L44" s="21"/>
+      <c r="A44" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="17"/>
+    </row>
+    <row r="45" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A45" s="49"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="19">
+        <f>SUM(J7:J44)</f>
+        <v>11.399999999999999</v>
+      </c>
+      <c r="K45" s="20">
+        <f>AVERAGE(K7:K44)</f>
+        <v>1</v>
+      </c>
+      <c r="L45" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A17:G17"/>
+  <mergeCells count="44">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -2695,7 +2831,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="7" width="8.69921875" style="10"/>
@@ -2707,15 +2843,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -2724,14 +2860,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -2740,14 +2876,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -2758,15 +2894,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -2784,257 +2920,525 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="14">
+      <c r="A7" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="37">
         <v>45995</v>
       </c>
-      <c r="I7" s="14">
-        <v>46011</v>
-      </c>
-      <c r="J7" s="36">
+      <c r="I7" s="37">
+        <v>45995</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="37">
+        <v>45999</v>
+      </c>
+      <c r="I8" s="37">
+        <v>46002</v>
+      </c>
+      <c r="J8" s="15">
+        <v>1</v>
+      </c>
+      <c r="K8" s="16">
+        <v>1</v>
+      </c>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="I9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="16">
+        <v>1</v>
+      </c>
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37">
+        <v>46006</v>
+      </c>
+      <c r="I10" s="37">
+        <v>46007</v>
+      </c>
+      <c r="J10" s="15">
+        <v>1</v>
+      </c>
+      <c r="K10" s="16">
+        <v>1</v>
+      </c>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37">
+        <v>46008</v>
+      </c>
+      <c r="I11" s="37">
+        <v>46009</v>
+      </c>
+      <c r="J11" s="15">
+        <v>1</v>
+      </c>
+      <c r="K11" s="16">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37">
         <v>46010</v>
       </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I8" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J8" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K8" s="16">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="55"/>
-    </row>
-    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I10" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J10" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K10" s="16">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="55"/>
-    </row>
-    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I12" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J12" s="36">
-        <v>46066</v>
+      <c r="I12" s="37">
+        <v>46010</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.5</v>
       </c>
       <c r="K12" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I13" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J13" s="36">
-        <v>46066</v>
+      <c r="A13" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="I13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.1</v>
       </c>
       <c r="K13" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="17"/>
     </row>
-    <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="55"/>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
+      <c r="A15" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="16">
+        <v>1</v>
+      </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
+      <c r="J16" s="36"/>
       <c r="K16" s="16"/>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19">
-        <f>SUM(J7:J16)</f>
-        <v>230274</v>
-      </c>
-      <c r="K17" s="20">
-        <f>AVERAGE(K7:K16)</f>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="17"/>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="17"/>
+    </row>
+    <row r="19" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="54"/>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>1</v>
+      </c>
+      <c r="L20" s="17"/>
+    </row>
+    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A24" s="69"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="54"/>
+    </row>
+    <row r="26" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A26" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="15">
         <v>0.2</v>
       </c>
-      <c r="L17" s="21"/>
+      <c r="K26" s="16">
+        <v>1</v>
+      </c>
+      <c r="L26" s="17"/>
+    </row>
+    <row r="27" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A27" s="69"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="17"/>
+    </row>
+    <row r="28" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="54"/>
+    </row>
+    <row r="29" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A29" s="69"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="17"/>
+    </row>
+    <row r="30" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A30" s="69"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A31" s="70"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="19">
+        <f>SUM(J7:J30)</f>
+        <v>5.1999999999999993</v>
+      </c>
+      <c r="K31" s="20">
+        <f>AVERAGE(K7:K30)</f>
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="L31" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A14:L14"/>
+  <mergeCells count="30">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3045,7 +3449,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="7" width="8.69921875" style="10"/>
@@ -3057,15 +3461,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -3074,14 +3478,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -3090,14 +3494,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -3108,15 +3512,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -3134,257 +3538,613 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="14">
+      <c r="A7" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="37">
         <v>45995</v>
       </c>
-      <c r="I7" s="14">
-        <v>46011</v>
-      </c>
-      <c r="J7" s="36">
+      <c r="I7" s="37">
+        <v>45995</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="37">
+        <v>45999</v>
+      </c>
+      <c r="I8" s="37">
+        <v>46002</v>
+      </c>
+      <c r="J8" s="15">
+        <v>1</v>
+      </c>
+      <c r="K8" s="16">
+        <v>1</v>
+      </c>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="I9" s="37">
+        <v>46003</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="16">
+        <v>1</v>
+      </c>
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37">
+        <v>46006</v>
+      </c>
+      <c r="I10" s="37">
+        <v>46007</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="16">
+        <v>1</v>
+      </c>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37">
+        <v>46008</v>
+      </c>
+      <c r="I11" s="37">
+        <v>46009</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="16">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37">
         <v>46010</v>
       </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I8" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J8" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K8" s="16">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="53" t="s">
+      <c r="I12" s="37">
+        <v>46010</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K12" s="16">
+        <v>1</v>
+      </c>
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="I13" s="37">
+        <v>46013</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="16">
+        <v>1</v>
+      </c>
+      <c r="L13" s="17"/>
+    </row>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K14" s="16">
+        <v>1</v>
+      </c>
+      <c r="L14" s="17"/>
+    </row>
+    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K15" s="16">
+        <v>1</v>
+      </c>
+      <c r="L15" s="17"/>
+    </row>
+    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K16" s="16">
+        <v>1</v>
+      </c>
+      <c r="L16" s="17"/>
+    </row>
+    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="16">
+        <v>1</v>
+      </c>
+      <c r="L17" s="17"/>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="16">
+        <v>1</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="K19" s="16">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>1</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="55"/>
-    </row>
-    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I10" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J10" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K10" s="16">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="53" t="s">
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="54"/>
+    </row>
+    <row r="22" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1</v>
+      </c>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K23" s="16">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A24" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="K24" s="16">
+        <v>1</v>
+      </c>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="55"/>
-    </row>
-    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I12" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J12" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K12" s="16">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="14">
-        <v>46012</v>
-      </c>
-      <c r="I13" s="14">
-        <v>46066</v>
-      </c>
-      <c r="J13" s="36">
-        <v>46066</v>
-      </c>
-      <c r="K13" s="16">
-        <v>0</v>
-      </c>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="54"/>
+    </row>
+    <row r="26" spans="1:12" ht="128.4" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="72" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="K26" s="39">
+        <v>1</v>
+      </c>
+      <c r="L26" s="17"/>
+    </row>
+    <row r="27" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="K27" s="39">
+        <v>1</v>
+      </c>
+      <c r="L27" s="17"/>
+    </row>
+    <row r="28" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="55"/>
-    </row>
-    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="17"/>
-    </row>
-    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19">
-        <f>SUM(J7:J16)</f>
-        <v>230274</v>
-      </c>
-      <c r="K17" s="20">
-        <f>AVERAGE(K7:K16)</f>
-        <v>0.2</v>
-      </c>
-      <c r="L17" s="21"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="54"/>
+    </row>
+    <row r="29" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A29" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="17"/>
+    </row>
+    <row r="30" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A30" s="69"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" ht="21" x14ac:dyDescent="0.6">
+      <c r="A31" s="70"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="19">
+        <f>SUM(J7:J30)</f>
+        <v>4.3999999999999995</v>
+      </c>
+      <c r="K31" s="20">
+        <f>AVERAGE(K7:K30)</f>
+        <v>1</v>
+      </c>
+      <c r="L31" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A14:L14"/>
+  <mergeCells count="30">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A23:G23"/>
     <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3396,7 +4156,7 @@
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.09765625" customWidth="1"/>
@@ -3404,12 +4164,12 @@
     <col min="7" max="7" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -3432,7 +4192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -3458,7 +4218,7 @@
       <c r="K4" s="27"/>
       <c r="L4" s="27"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -3483,7 +4243,7 @@
       <c r="K5" s="27"/>
       <c r="L5" s="27"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -3508,7 +4268,7 @@
       <c r="K6" s="27"/>
       <c r="L6" s="27"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -3534,7 +4294,7 @@
       <c r="K7" s="27"/>
       <c r="L7" s="27"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="30" t="s">
         <v>32</v>
@@ -3552,7 +4312,7 @@
       <c r="K8" s="27"/>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="30" t="s">
         <v>34</v>
@@ -3570,7 +4330,7 @@
       <c r="K9" s="27"/>
       <c r="L9" s="27"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="30" t="s">
         <v>33</v>
@@ -3588,7 +4348,7 @@
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -3613,7 +4373,7 @@
       <c r="K11" s="27"/>
       <c r="L11" s="27"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -3638,7 +4398,7 @@
       <c r="K12" s="27"/>
       <c r="L12" s="27"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -3663,7 +4423,7 @@
       <c r="K13" s="27"/>
       <c r="L13" s="27"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -3686,7 +4446,7 @@
       <c r="K14" s="27"/>
       <c r="L14" s="27"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="D15" s="27"/>
       <c r="E15" s="27"/>
@@ -3695,66 +4455,66 @@
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H17" s="28"/>
       <c r="J17" s="28"/>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H18" s="28"/>
       <c r="J18" s="28"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="28"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="28"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="28"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="28"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="28"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="28"/>
     </row>
   </sheetData>
@@ -3779,15 +4539,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -3796,14 +4556,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -3812,14 +4572,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -3830,15 +4590,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -3856,29 +4616,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="15">
@@ -3888,13 +4648,13 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
+      <c r="A8" s="69"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -3902,29 +4662,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="55"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="54"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -3932,29 +4692,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="55"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="54"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -3962,13 +4722,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -3976,29 +4736,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="55"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -4006,13 +4766,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -4020,13 +4780,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -4041,6 +4801,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
@@ -4051,12 +4817,6 @@
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4079,15 +4839,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -4096,14 +4856,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -4112,14 +4872,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -4130,15 +4890,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -4156,29 +4916,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="15"/>
@@ -4186,13 +4946,13 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
+      <c r="A8" s="69"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -4200,29 +4960,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="55"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="54"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -4230,29 +4990,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="55"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="54"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -4260,13 +5020,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -4274,29 +5034,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="55"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -4304,13 +5064,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -4318,13 +5078,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -4339,6 +5099,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
@@ -4349,12 +5115,6 @@
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4377,15 +5137,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="10"/>
@@ -4394,14 +5154,14 @@
       <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="K2" s="10"/>
@@ -4410,14 +5170,14 @@
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="61">
+        <v>1</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
       <c r="K3" s="10"/>
@@ -4428,15 +5188,15 @@
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:12" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="12" t="s">
         <v>39</v>
       </c>
@@ -4454,29 +5214,29 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="15"/>
@@ -4484,13 +5244,13 @@
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
+      <c r="A8" s="69"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
@@ -4498,29 +5258,29 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="55"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="54"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="15"/>
@@ -4528,29 +5288,29 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="55"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="54"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
@@ -4558,13 +5318,13 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
@@ -4572,29 +5332,29 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="55"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
@@ -4602,13 +5362,13 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -4616,13 +5376,13 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="63"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="19">
@@ -4637,6 +5397,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
@@ -4647,12 +5413,6 @@
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
